--- a/51kernel.xlsx
+++ b/51kernel.xlsx
@@ -426,7 +426,7 @@
         <v>0.009006</v>
       </c>
       <c r="H2" s="1">
-        <v>0.025026</v>
+        <v>0.033015</v>
       </c>
       <c r="I2" s="1">
         <v>0.002987</v>
@@ -453,7 +453,7 @@
       </c>
       <c r="O2" s="4">
         <f t="shared" si="1"/>
-        <v>0.03121753376</v>
+        <v>0.02366348629</v>
       </c>
       <c r="P2" s="4">
         <f t="shared" si="1"/>
@@ -481,7 +481,7 @@
       </c>
       <c r="V2" s="4">
         <f t="shared" si="2"/>
-        <v>1.997922161</v>
+        <v>1.514463123</v>
       </c>
       <c r="W2" s="4">
         <f t="shared" si="2"/>
@@ -515,7 +515,7 @@
         <v>0.027405</v>
       </c>
       <c r="H3" s="1">
-        <v>0.037585</v>
+        <v>0.057106</v>
       </c>
       <c r="I3" s="1">
         <v>0.011909</v>
@@ -542,7 +542,7 @@
       </c>
       <c r="O3" s="4">
         <f t="shared" si="3"/>
-        <v>0.07483038446</v>
+        <v>0.04925051658</v>
       </c>
       <c r="P3" s="4">
         <f t="shared" si="3"/>
@@ -570,7 +570,7 @@
       </c>
       <c r="V3" s="4">
         <f t="shared" si="4"/>
-        <v>4.789144606</v>
+        <v>3.152033061</v>
       </c>
       <c r="W3" s="4">
         <f t="shared" si="4"/>
@@ -604,7 +604,7 @@
         <v>0.099816</v>
       </c>
       <c r="H4" s="1">
-        <v>0.074544</v>
+        <v>0.154398</v>
       </c>
       <c r="I4" s="1">
         <v>0.037527</v>
@@ -631,7 +631,7 @@
       </c>
       <c r="O4" s="4">
         <f t="shared" si="6"/>
-        <v>0.1488215014</v>
+        <v>0.07185164316</v>
       </c>
       <c r="P4" s="4">
         <f t="shared" si="6"/>
@@ -659,7 +659,7 @@
       </c>
       <c r="V4" s="4">
         <f t="shared" si="7"/>
-        <v>9.524576089</v>
+        <v>4.598505162</v>
       </c>
       <c r="W4" s="4">
         <f t="shared" si="7"/>
@@ -693,7 +693,7 @@
         <v>0.365534</v>
       </c>
       <c r="H5" s="1">
-        <v>0.16365</v>
+        <v>0.455827</v>
       </c>
       <c r="I5" s="1">
         <v>0.131466</v>
@@ -720,7 +720,7 @@
       </c>
       <c r="O5" s="4">
         <f t="shared" si="8"/>
-        <v>0.2807057745</v>
+        <v>0.1007783655</v>
       </c>
       <c r="P5" s="4">
         <f t="shared" si="8"/>
@@ -748,7 +748,7 @@
       </c>
       <c r="V5" s="4">
         <f t="shared" si="9"/>
-        <v>17.96516957</v>
+        <v>6.44981539</v>
       </c>
       <c r="W5" s="4">
         <f t="shared" si="9"/>
@@ -782,7 +782,7 @@
         <v>1.4011</v>
       </c>
       <c r="H6" s="1">
-        <v>0.505639</v>
+        <v>1.640868</v>
       </c>
       <c r="I6" s="1">
         <v>0.501472</v>
@@ -809,7 +809,7 @@
       </c>
       <c r="O6" s="4">
         <f t="shared" si="10"/>
-        <v>0.3618564826</v>
+        <v>0.1115072937</v>
       </c>
       <c r="P6" s="4">
         <f t="shared" si="10"/>
@@ -837,7 +837,7 @@
       </c>
       <c r="V6" s="4">
         <f t="shared" si="11"/>
-        <v>23.15881489</v>
+        <v>7.136466797</v>
       </c>
       <c r="W6" s="4">
         <f t="shared" si="11"/>
@@ -871,7 +871,7 @@
         <v>5.518049</v>
       </c>
       <c r="H7" s="1">
-        <v>1.632777</v>
+        <v>4.723325</v>
       </c>
       <c r="I7" s="1">
         <v>1.91466</v>
@@ -898,7 +898,7 @@
       </c>
       <c r="O7" s="4">
         <f t="shared" si="12"/>
-        <v>0.4493877609</v>
+        <v>0.1553460751</v>
       </c>
       <c r="P7" s="4">
         <f t="shared" si="12"/>
@@ -926,7 +926,7 @@
       </c>
       <c r="V7" s="4">
         <f t="shared" si="13"/>
-        <v>28.76081669</v>
+        <v>9.942148804</v>
       </c>
       <c r="W7" s="4">
         <f t="shared" si="13"/>
@@ -960,7 +960,7 @@
         <v>21.744773</v>
       </c>
       <c r="H8" s="1">
-        <v>5.628886</v>
+        <v>17.940789</v>
       </c>
       <c r="I8" s="1">
         <v>7.545497</v>
@@ -987,7 +987,7 @@
       </c>
       <c r="O8" s="4">
         <f t="shared" si="14"/>
-        <v>0.523110834</v>
+        <v>0.1641249585</v>
       </c>
       <c r="P8" s="4">
         <f t="shared" si="14"/>
@@ -1015,7 +1015,7 @@
       </c>
       <c r="V8" s="4">
         <f t="shared" si="15"/>
-        <v>33.47909338</v>
+        <v>10.50399734</v>
       </c>
       <c r="W8" s="4">
         <f t="shared" si="15"/>
@@ -1049,7 +1049,7 @@
         <v>86.06999</v>
       </c>
       <c r="H9" s="1">
-        <v>20.605076</v>
+        <v>72.491659</v>
       </c>
       <c r="I9" s="1">
         <v>29.620067</v>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="O9" s="4">
         <f t="shared" si="16"/>
-        <v>0.5721284406</v>
+        <v>0.1626221577</v>
       </c>
       <c r="P9" s="4">
         <f t="shared" si="16"/>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="V9" s="4">
         <f t="shared" si="17"/>
-        <v>36.6162202</v>
+        <v>10.40781809</v>
       </c>
       <c r="W9" s="4">
         <f t="shared" si="17"/>
